--- a/VT_KiNESYS_NewElc_V6.xlsx
+++ b/VT_KiNESYS_NewElc_V6.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="4"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="veda - techs" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="veda - flows" sheetId="3" r:id="rId3"/>
     <sheet name="CO2 trans and sto" sheetId="4" r:id="rId4"/>
     <sheet name="provenance" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="303">
   <si>
     <t>~FI_T</t>
   </si>
@@ -778,6 +779,168 @@
   </si>
   <si>
     <t>source: en_wind_onshore</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>CommName</t>
+  </si>
+  <si>
+    <t>Timeslices</t>
+  </si>
+  <si>
+    <t>AllRegions</t>
+  </si>
+  <si>
+    <t>COM_FR</t>
+  </si>
+  <si>
+    <t>ELCDem</t>
+  </si>
+  <si>
+    <t>S1H1</t>
+  </si>
+  <si>
+    <t>S1H2</t>
+  </si>
+  <si>
+    <t>S1H3</t>
+  </si>
+  <si>
+    <t>S1H4</t>
+  </si>
+  <si>
+    <t>S1H5</t>
+  </si>
+  <si>
+    <t>S1H6</t>
+  </si>
+  <si>
+    <t>S1H7</t>
+  </si>
+  <si>
+    <t>S1H8</t>
+  </si>
+  <si>
+    <t>S2H1</t>
+  </si>
+  <si>
+    <t>S2H2</t>
+  </si>
+  <si>
+    <t>S2H3</t>
+  </si>
+  <si>
+    <t>S2H4</t>
+  </si>
+  <si>
+    <t>S2H5</t>
+  </si>
+  <si>
+    <t>S2H6</t>
+  </si>
+  <si>
+    <t>S2H7</t>
+  </si>
+  <si>
+    <t>S2H8</t>
+  </si>
+  <si>
+    <t>S3H1</t>
+  </si>
+  <si>
+    <t>S3H2</t>
+  </si>
+  <si>
+    <t>S3H3</t>
+  </si>
+  <si>
+    <t>S3H4</t>
+  </si>
+  <si>
+    <t>S3H5</t>
+  </si>
+  <si>
+    <t>S3H6</t>
+  </si>
+  <si>
+    <t>S3H7</t>
+  </si>
+  <si>
+    <t>S3H8</t>
+  </si>
+  <si>
+    <t>S4H1</t>
+  </si>
+  <si>
+    <t>S4H2</t>
+  </si>
+  <si>
+    <t>S4H3</t>
+  </si>
+  <si>
+    <t>S4H4</t>
+  </si>
+  <si>
+    <t>S4H5</t>
+  </si>
+  <si>
+    <t>S4H6</t>
+  </si>
+  <si>
+    <t>S4H7</t>
+  </si>
+  <si>
+    <t>S4H8</t>
+  </si>
+  <si>
+    <t>S5H1</t>
+  </si>
+  <si>
+    <t>S5H2</t>
+  </si>
+  <si>
+    <t>S5H3</t>
+  </si>
+  <si>
+    <t>S5H4</t>
+  </si>
+  <si>
+    <t>S5H5</t>
+  </si>
+  <si>
+    <t>S5H6</t>
+  </si>
+  <si>
+    <t>S5H7</t>
+  </si>
+  <si>
+    <t>S5H8</t>
+  </si>
+  <si>
+    <t>S6H1</t>
+  </si>
+  <si>
+    <t>S6H2</t>
+  </si>
+  <si>
+    <t>S6H3</t>
+  </si>
+  <si>
+    <t>S6H4</t>
+  </si>
+  <si>
+    <t>S6H5</t>
+  </si>
+  <si>
+    <t>S6H6</t>
+  </si>
+  <si>
+    <t>S6H7</t>
+  </si>
+  <si>
+    <t>S6H8</t>
   </si>
 </sst>
 </file>
@@ -790,10 +953,17 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -943,12 +1113,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1267,16 +1443,13 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1285,37 +1458,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1330,77 +1503,83 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2621,7 +2800,7 @@
       <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="5">
         <v>2200</v>
       </c>
       <c r="L25" t="s">
@@ -2668,7 +2847,7 @@
       <c r="H26">
         <v>1</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="5">
         <v>2200</v>
       </c>
       <c r="L26" t="s">
@@ -16586,7 +16765,7 @@
       <c r="A6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>46272</v>
       </c>
     </row>
@@ -17284,4 +17463,713 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.037057043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.01431031</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.031935713</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.031333153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.015967293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.008888083</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.025307249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.01431031</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.032602373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.012590036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.028096701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.027566575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.014047829</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.007819075</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.022264484</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.012590036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.032675781</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.012618696</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.028159616</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.027628302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.014079808</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.007836311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.022314633</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.012618696</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.036459292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.014079808</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.031420203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.030827369</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.015710101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.008743674</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.024898433</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.014079808</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.03508347</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.013548494</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.030234535</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.029664072</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.015117267</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.008413724</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.023958869</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.013548494</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.033019736</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.012751524</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.028456033</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.027919127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.014228016</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.007918799</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.022549524</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.012751524</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/VT_KiNESYS_NewElc_V6.xlsx
+++ b/VT_KiNESYS_NewElc_V6.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4"/>
   </bookViews>
   <sheets>
     <sheet name="veda - techs" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="249">
   <si>
     <t>~FI_T</t>
   </si>
@@ -779,168 +779,6 @@
   </si>
   <si>
     <t>source: en_wind_onshore</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>CommName</t>
-  </si>
-  <si>
-    <t>Timeslices</t>
-  </si>
-  <si>
-    <t>AllRegions</t>
-  </si>
-  <si>
-    <t>COM_FR</t>
-  </si>
-  <si>
-    <t>ELCDem</t>
-  </si>
-  <si>
-    <t>S1H1</t>
-  </si>
-  <si>
-    <t>S1H2</t>
-  </si>
-  <si>
-    <t>S1H3</t>
-  </si>
-  <si>
-    <t>S1H4</t>
-  </si>
-  <si>
-    <t>S1H5</t>
-  </si>
-  <si>
-    <t>S1H6</t>
-  </si>
-  <si>
-    <t>S1H7</t>
-  </si>
-  <si>
-    <t>S1H8</t>
-  </si>
-  <si>
-    <t>S2H1</t>
-  </si>
-  <si>
-    <t>S2H2</t>
-  </si>
-  <si>
-    <t>S2H3</t>
-  </si>
-  <si>
-    <t>S2H4</t>
-  </si>
-  <si>
-    <t>S2H5</t>
-  </si>
-  <si>
-    <t>S2H6</t>
-  </si>
-  <si>
-    <t>S2H7</t>
-  </si>
-  <si>
-    <t>S2H8</t>
-  </si>
-  <si>
-    <t>S3H1</t>
-  </si>
-  <si>
-    <t>S3H2</t>
-  </si>
-  <si>
-    <t>S3H3</t>
-  </si>
-  <si>
-    <t>S3H4</t>
-  </si>
-  <si>
-    <t>S3H5</t>
-  </si>
-  <si>
-    <t>S3H6</t>
-  </si>
-  <si>
-    <t>S3H7</t>
-  </si>
-  <si>
-    <t>S3H8</t>
-  </si>
-  <si>
-    <t>S4H1</t>
-  </si>
-  <si>
-    <t>S4H2</t>
-  </si>
-  <si>
-    <t>S4H3</t>
-  </si>
-  <si>
-    <t>S4H4</t>
-  </si>
-  <si>
-    <t>S4H5</t>
-  </si>
-  <si>
-    <t>S4H6</t>
-  </si>
-  <si>
-    <t>S4H7</t>
-  </si>
-  <si>
-    <t>S4H8</t>
-  </si>
-  <si>
-    <t>S5H1</t>
-  </si>
-  <si>
-    <t>S5H2</t>
-  </si>
-  <si>
-    <t>S5H3</t>
-  </si>
-  <si>
-    <t>S5H4</t>
-  </si>
-  <si>
-    <t>S5H5</t>
-  </si>
-  <si>
-    <t>S5H6</t>
-  </si>
-  <si>
-    <t>S5H7</t>
-  </si>
-  <si>
-    <t>S5H8</t>
-  </si>
-  <si>
-    <t>S6H1</t>
-  </si>
-  <si>
-    <t>S6H2</t>
-  </si>
-  <si>
-    <t>S6H3</t>
-  </si>
-  <si>
-    <t>S6H4</t>
-  </si>
-  <si>
-    <t>S6H5</t>
-  </si>
-  <si>
-    <t>S6H6</t>
-  </si>
-  <si>
-    <t>S6H7</t>
-  </si>
-  <si>
-    <t>S6H8</t>
   </si>
 </sst>
 </file>
@@ -953,17 +791,10 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1113,18 +944,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1443,13 +1268,16 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1458,37 +1286,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1503,83 +1331,77 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2800,7 +2622,7 @@
       <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="2">
         <v>2200</v>
       </c>
       <c r="L25" t="s">
@@ -2847,7 +2669,7 @@
       <c r="H26">
         <v>1</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="2">
         <v>2200</v>
       </c>
       <c r="L26" t="s">
@@ -16765,7 +16587,7 @@
       <c r="A6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="1">
         <v>46272</v>
       </c>
     </row>
@@ -17468,707 +17290,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.16666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="11.1666666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.037057043</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.01431031</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.031935713</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.031333153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.015967293</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.008888083</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.025307249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.01431031</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.032602373</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.012590036</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.028096701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.027566575</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.014047829</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0.007819075</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0.022264484</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0.012590036</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.032675781</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0.012618696</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0.028159616</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0.027628302</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.014079808</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0.007836311</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.022314633</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0.012618696</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0.036459292</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0.014079808</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.031420203</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.030827369</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0.015710101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0.008743674</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0.024898433</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.014079808</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.03508347</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0.013548494</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.030234535</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0.029664072</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0.015117267</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.008413724</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0.023958869</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.013548494</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0.033019736</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0.012751524</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0.028456033</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D46" s="1">
-        <v>0.027919127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.014228016</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0.007918799</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0.022549524</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.012751524</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
